--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127369233</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684759</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685077</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688411</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134526179</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323669</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323673</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127369215</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685847</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686212</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134526250</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2016,6 +2081,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133691196</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2155,6 +2225,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134526138</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686095</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686179</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2456,6 +2541,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684468</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2553,6 +2643,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684672</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2650,6 +2745,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688743</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2747,6 +2847,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323536</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2844,6 +2949,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323566</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689779</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3038,6 +3153,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323480</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127324095</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3232,6 +3357,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686251</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3358,6 +3488,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530339</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3484,6 +3619,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134525785</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3581,6 +3721,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323353</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3678,6 +3823,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323284</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3775,6 +3925,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686261</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3872,6 +4027,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323834</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3969,6 +4129,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323921</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4066,6 +4231,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323931</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4163,6 +4333,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323933</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4260,6 +4435,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684870</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4357,6 +4537,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685839</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4459,6 +4644,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688661</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4556,6 +4746,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689273</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4653,6 +4848,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689338</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4779,6 +4979,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134526038</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4876,6 +5081,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127324159</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4987,6 +5197,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134525868</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5084,6 +5299,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127324353</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5181,6 +5401,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323728</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5287,6 +5512,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323767</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5384,6 +5614,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323861</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5481,6 +5716,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323877</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5597,6 +5837,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323884</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5694,6 +5939,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323904</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5791,6 +6041,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323912</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5888,6 +6143,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323923</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5985,6 +6245,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323993</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6082,6 +6347,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127324058</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6179,6 +6449,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127324130</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6276,6 +6551,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685659</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6382,6 +6662,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685747</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6479,6 +6764,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685866</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6585,6 +6875,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685908</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6691,6 +6986,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688499</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6788,6 +7088,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688781</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6885,6 +7190,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688863</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6982,6 +7292,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688890</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7079,6 +7394,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689429</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7176,6 +7496,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689512</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7282,6 +7607,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689901</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7379,6 +7709,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133690721</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7476,6 +7811,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133691269</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7573,6 +7913,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669713</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7679,6 +8024,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134914999</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7776,6 +8126,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323126</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7873,6 +8228,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688678</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7994,6 +8354,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530183</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8091,6 +8456,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323374</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8188,6 +8558,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386811</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8309,6 +8684,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530306</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8430,8 +8810,91 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134526048</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ77"/>
+  <dimension ref="A1:AZ103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3365,51 +3365,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134530339</v>
+        <v>135651460</v>
       </c>
       <c r="B27" t="n">
-        <v>75468</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477164</v>
+        <v>477124</v>
       </c>
       <c r="R27" t="n">
-        <v>6854653</v>
+        <v>6854444</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3433,12 +3430,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,100 +3444,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>i kanten av lok # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134530339</t>
+          <t>https://artportalen.se/Sighting/135651460</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134525785</v>
+        <v>135651610</v>
       </c>
       <c r="B28" t="n">
-        <v>75340</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477229</v>
+        <v>477101</v>
       </c>
       <c r="R28" t="n">
-        <v>6854414</v>
+        <v>6854442</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3564,12 +3532,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,81 +3546,55 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134525785</t>
+          <t>https://artportalen.se/Sighting/135651610</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127323353</v>
+        <v>135651722</v>
       </c>
       <c r="B29" t="n">
-        <v>78730</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3662,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476938</v>
+        <v>477110</v>
       </c>
       <c r="R29" t="n">
-        <v>6854905</v>
+        <v>6854461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3692,12 +3634,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,49 +3654,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323353</t>
+          <t>https://artportalen.se/Sighting/135651722</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127323284</v>
+        <v>135652158</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3764,13 +3706,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476946</v>
+        <v>477131</v>
       </c>
       <c r="R30" t="n">
-        <v>6854917</v>
+        <v>6854528</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3794,12 +3736,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3814,27 +3756,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323284</t>
+          <t>https://artportalen.se/Sighting/135652158</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133686261</v>
+        <v>134530339</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>75468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,37 +3784,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477266</v>
+        <v>477164</v>
       </c>
       <c r="R31" t="n">
-        <v>6854496</v>
+        <v>6854653</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3910,71 +3855,100 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>i kanten av lok # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133686261</t>
+          <t>https://artportalen.se/Sighting/134530339</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127323834</v>
+        <v>134525785</v>
       </c>
       <c r="B32" t="n">
-        <v>80432</v>
+        <v>75340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477019</v>
+        <v>477229</v>
       </c>
       <c r="R32" t="n">
-        <v>6854759</v>
+        <v>6854414</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3998,12 +3972,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,33 +3986,59 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323834</t>
+          <t>https://artportalen.se/Sighting/134525785</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127323921</v>
+        <v>127323353</v>
       </c>
       <c r="B33" t="n">
-        <v>80432</v>
+        <v>78730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477064</v>
+        <v>476938</v>
       </c>
       <c r="R33" t="n">
-        <v>6854729</v>
+        <v>6854905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,16 +4131,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323921</t>
+          <t>https://artportalen.se/Sighting/127323353</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127323931</v>
+        <v>135651380</v>
       </c>
       <c r="B34" t="n">
-        <v>80432</v>
+        <v>79168</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,34 +4148,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477063</v>
+        <v>477131</v>
       </c>
       <c r="R34" t="n">
-        <v>6854712</v>
+        <v>6854439</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4222,27 +4222,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323931</t>
+          <t>https://artportalen.se/Sighting/135651380</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127323933</v>
+        <v>127323284</v>
       </c>
       <c r="B35" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477031</v>
+        <v>476946</v>
       </c>
       <c r="R35" t="n">
-        <v>6854762</v>
+        <v>6854917</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4324,27 +4324,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323933</t>
+          <t>https://artportalen.se/Sighting/127323284</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133684870</v>
+        <v>133686261</v>
       </c>
       <c r="B36" t="n">
-        <v>80488</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4352,37 +4352,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477230</v>
+        <v>477266</v>
       </c>
       <c r="R36" t="n">
-        <v>6854415</v>
+        <v>6854496</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4426,27 +4426,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133684870</t>
+          <t>https://artportalen.se/Sighting/133686261</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133685839</v>
+        <v>135651365</v>
       </c>
       <c r="B37" t="n">
-        <v>80488</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,34 +4454,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477222</v>
+        <v>477137</v>
       </c>
       <c r="R37" t="n">
-        <v>6854404</v>
+        <v>6854442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4539,16 +4539,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685839</t>
+          <t>https://artportalen.se/Sighting/135651365</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133688661</v>
+        <v>127323834</v>
       </c>
       <c r="B38" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477281</v>
+        <v>477019</v>
       </c>
       <c r="R38" t="n">
-        <v>6854562</v>
+        <v>6854759</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,17 +4610,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4635,27 +4630,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688661</t>
+          <t>https://artportalen.se/Sighting/127323834</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133689273</v>
+        <v>127323921</v>
       </c>
       <c r="B39" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4687,10 +4682,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477171</v>
+        <v>477064</v>
       </c>
       <c r="R39" t="n">
-        <v>6854572</v>
+        <v>6854729</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,12 +4712,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,27 +4732,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689273</t>
+          <t>https://artportalen.se/Sighting/127323921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133689338</v>
+        <v>127323931</v>
       </c>
       <c r="B40" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477202</v>
+        <v>477063</v>
       </c>
       <c r="R40" t="n">
-        <v>6854583</v>
+        <v>6854712</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4819,12 +4814,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4839,27 +4834,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689338</t>
+          <t>https://artportalen.se/Sighting/127323931</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134526038</v>
+        <v>127323933</v>
       </c>
       <c r="B41" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4885,22 +4880,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477204</v>
+        <v>477031</v>
       </c>
       <c r="R41" t="n">
-        <v>6854574</v>
+        <v>6854762</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4924,12 +4916,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4938,81 +4930,55 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>vid lok # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134526038</t>
+          <t>https://artportalen.se/Sighting/127323933</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127324159</v>
+        <v>133684870</v>
       </c>
       <c r="B42" t="n">
-        <v>80460</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5022,13 +4988,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477033</v>
+        <v>477230</v>
       </c>
       <c r="R42" t="n">
-        <v>6854650</v>
+        <v>6854415</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5052,12 +5018,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5083,57 +5049,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324159</t>
+          <t>https://artportalen.se/Sighting/133684870</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134525868</v>
+        <v>133685839</v>
       </c>
       <c r="B43" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477321</v>
+        <v>477222</v>
       </c>
       <c r="R43" t="n">
-        <v>6854556</v>
+        <v>6854404</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5171,44 +5134,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134525868</t>
+          <t>https://artportalen.se/Sighting/133685839</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127324353</v>
+        <v>133688661</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5216,37 +5168,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477164</v>
+        <v>477281</v>
       </c>
       <c r="R44" t="n">
-        <v>6854349</v>
+        <v>6854562</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5270,12 +5222,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,38 +5258,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324353</t>
+          <t>https://artportalen.se/Sighting/133688661</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127323728</v>
+        <v>133689273</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5342,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476992</v>
+        <v>477171</v>
       </c>
       <c r="R45" t="n">
-        <v>6854784</v>
+        <v>6854572</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5392,71 +5349,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323728</t>
+          <t>https://artportalen.se/Sighting/133689273</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127323767</v>
+        <v>133689338</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476962</v>
+        <v>477202</v>
       </c>
       <c r="R46" t="n">
-        <v>6854787</v>
+        <v>6854583</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5483,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5514,54 +5462,57 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323767</t>
+          <t>https://artportalen.se/Sighting/133689338</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127323861</v>
+        <v>134526038</v>
       </c>
       <c r="B47" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476993</v>
+        <v>477204</v>
       </c>
       <c r="R47" t="n">
-        <v>6854793</v>
+        <v>6854574</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5585,12 +5536,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5599,55 +5550,81 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>vid lok # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323861</t>
+          <t>https://artportalen.se/Sighting/134526038</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127323877</v>
+        <v>135652113</v>
       </c>
       <c r="B48" t="n">
-        <v>99118</v>
+        <v>80526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,13 +5634,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476997</v>
+        <v>477139</v>
       </c>
       <c r="R48" t="n">
-        <v>6854787</v>
+        <v>6854519</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5687,12 +5664,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,68 +5695,54 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323877</t>
+          <t>https://artportalen.se/Sighting/135652113</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127323884</v>
+        <v>135652154</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>80526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477019</v>
+        <v>477131</v>
       </c>
       <c r="R49" t="n">
-        <v>6854759</v>
+        <v>6854528</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5803,17 +5766,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ljusa blad. Kantzonseffekt vid väg.</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,49 +5786,49 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323884</t>
+          <t>https://artportalen.se/Sighting/135652154</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127323904</v>
+        <v>127324159</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>80460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5880,10 +5838,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477003</v>
+        <v>477033</v>
       </c>
       <c r="R50" t="n">
-        <v>6854772</v>
+        <v>6854650</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5941,54 +5899,57 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323904</t>
+          <t>https://artportalen.se/Sighting/127324159</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127323912</v>
+        <v>134525868</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>80492</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477010</v>
+        <v>477321</v>
       </c>
       <c r="R51" t="n">
-        <v>6854772</v>
+        <v>6854556</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6012,12 +5973,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,71 +5987,82 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323912</t>
+          <t>https://artportalen.se/Sighting/134525868</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127323923</v>
+        <v>127324353</v>
       </c>
       <c r="B52" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477014</v>
+        <v>477164</v>
       </c>
       <c r="R52" t="n">
-        <v>6854772</v>
+        <v>6854349</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6145,54 +6117,54 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323923</t>
+          <t>https://artportalen.se/Sighting/127324353</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127323993</v>
+        <v>135652838</v>
       </c>
       <c r="B53" t="n">
-        <v>99118</v>
+        <v>41610</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>215713</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477076</v>
+        <v>477139</v>
       </c>
       <c r="R53" t="n">
-        <v>6854706</v>
+        <v>6854377</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6216,12 +6188,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6236,65 +6213,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323993</t>
+          <t>https://artportalen.se/Sighting/135652838</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127324058</v>
+        <v>135653121</v>
       </c>
       <c r="B54" t="n">
-        <v>99118</v>
+        <v>42875</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>216248</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Baltiskt skogsfly</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Xestia baltica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Valle, 1940)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477039</v>
+        <v>477097</v>
       </c>
       <c r="R54" t="n">
-        <v>6854676</v>
+        <v>6854375</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6318,12 +6295,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,54 +6326,54 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324058</t>
+          <t>https://artportalen.se/Sighting/135653121</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127324130</v>
+        <v>135653167</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>42870</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>216255</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödfläckigt jordfly</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Xestia alpicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Zetterstedt, 1839)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477037</v>
+        <v>477098</v>
       </c>
       <c r="R55" t="n">
-        <v>6854645</v>
+        <v>6854370</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,12 +6397,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6451,16 +6428,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324130</t>
+          <t>https://artportalen.se/Sighting/135653167</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133685659</v>
+        <v>127323728</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,10 +6469,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477222</v>
+        <v>476992</v>
       </c>
       <c r="R56" t="n">
-        <v>6854402</v>
+        <v>6854784</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6522,12 +6499,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6542,27 +6519,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685659</t>
+          <t>https://artportalen.se/Sighting/127323728</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133685747</v>
+        <v>127323767</v>
       </c>
       <c r="B57" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6589,7 +6566,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6603,10 +6580,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477222</v>
+        <v>476962</v>
       </c>
       <c r="R57" t="n">
-        <v>6854404</v>
+        <v>6854787</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6633,12 +6610,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6664,16 +6641,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685747</t>
+          <t>https://artportalen.se/Sighting/127323767</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133685866</v>
+        <v>127323861</v>
       </c>
       <c r="B58" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6701,17 +6678,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477215</v>
+        <v>476993</v>
       </c>
       <c r="R58" t="n">
-        <v>6854428</v>
+        <v>6854793</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6735,12 +6712,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6766,16 +6743,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685866</t>
+          <t>https://artportalen.se/Sighting/127323861</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133685908</v>
+        <v>127323877</v>
       </c>
       <c r="B59" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,29 +6777,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477218</v>
+        <v>476997</v>
       </c>
       <c r="R59" t="n">
-        <v>6854443</v>
+        <v>6854787</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6846,12 +6814,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6877,16 +6845,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685908</t>
+          <t>https://artportalen.se/Sighting/127323877</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133688499</v>
+        <v>127323884</v>
       </c>
       <c r="B60" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6913,7 +6881,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6921,19 +6889,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477281</v>
+        <v>477019</v>
       </c>
       <c r="R60" t="n">
-        <v>6854562</v>
+        <v>6854759</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6957,12 +6930,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ljusa blad. Kantzonseffekt vid väg.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,27 +6955,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688499</t>
+          <t>https://artportalen.se/Sighting/127323884</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133688781</v>
+        <v>127323904</v>
       </c>
       <c r="B61" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7029,13 +7007,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477266</v>
+        <v>477003</v>
       </c>
       <c r="R61" t="n">
-        <v>6854565</v>
+        <v>6854772</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7059,12 +7037,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7090,16 +7068,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688781</t>
+          <t>https://artportalen.se/Sighting/127323904</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133688863</v>
+        <v>127323912</v>
       </c>
       <c r="B62" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7131,13 +7109,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477250</v>
+        <v>477010</v>
       </c>
       <c r="R62" t="n">
-        <v>6854562</v>
+        <v>6854772</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7161,12 +7139,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7192,16 +7170,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688863</t>
+          <t>https://artportalen.se/Sighting/127323912</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133688890</v>
+        <v>127323923</v>
       </c>
       <c r="B63" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,10 +7211,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477239</v>
+        <v>477014</v>
       </c>
       <c r="R63" t="n">
-        <v>6854556</v>
+        <v>6854772</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7263,12 +7241,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7294,16 +7272,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688890</t>
+          <t>https://artportalen.se/Sighting/127323923</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133689429</v>
+        <v>127323993</v>
       </c>
       <c r="B64" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7335,13 +7313,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477202</v>
+        <v>477076</v>
       </c>
       <c r="R64" t="n">
-        <v>6854583</v>
+        <v>6854706</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7365,12 +7343,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7385,27 +7363,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689429</t>
+          <t>https://artportalen.se/Sighting/127323993</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133689512</v>
+        <v>127324058</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7433,17 +7411,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477213</v>
+        <v>477039</v>
       </c>
       <c r="R65" t="n">
-        <v>6854605</v>
+        <v>6854676</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7467,12 +7445,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7498,16 +7476,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689512</t>
+          <t>https://artportalen.se/Sighting/127324058</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133689901</v>
+        <v>127324130</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7532,29 +7510,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477179</v>
+        <v>477037</v>
       </c>
       <c r="R66" t="n">
-        <v>6854626</v>
+        <v>6854645</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7578,12 +7547,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7609,13 +7578,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689901</t>
+          <t>https://artportalen.se/Sighting/127324130</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133690721</v>
+        <v>133685659</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -7650,10 +7619,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477168</v>
+        <v>477222</v>
       </c>
       <c r="R67" t="n">
-        <v>6854646</v>
+        <v>6854402</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7711,13 +7680,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133690721</t>
+          <t>https://artportalen.se/Sighting/133685659</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133691269</v>
+        <v>133685747</v>
       </c>
       <c r="B68" t="n">
         <v>99195</v>
@@ -7745,17 +7714,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477132</v>
+        <v>477222</v>
       </c>
       <c r="R68" t="n">
-        <v>6854710</v>
+        <v>6854404</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7813,13 +7791,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133691269</t>
+          <t>https://artportalen.se/Sighting/133685747</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134669713</v>
+        <v>133685866</v>
       </c>
       <c r="B69" t="n">
         <v>99195</v>
@@ -7854,10 +7832,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477098</v>
+        <v>477215</v>
       </c>
       <c r="R69" t="n">
-        <v>6854401</v>
+        <v>6854428</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7884,12 +7862,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7915,13 +7893,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134669713</t>
+          <t>https://artportalen.se/Sighting/133685866</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134914999</v>
+        <v>133685908</v>
       </c>
       <c r="B70" t="n">
         <v>99195</v>
@@ -7951,7 +7929,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7965,10 +7943,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477113</v>
+        <v>477218</v>
       </c>
       <c r="R70" t="n">
-        <v>6854388</v>
+        <v>6854443</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7995,12 +7973,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8026,54 +8004,63 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134914999</t>
+          <t>https://artportalen.se/Sighting/133685908</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127323126</v>
+        <v>133688499</v>
       </c>
       <c r="B71" t="n">
-        <v>79085</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476950</v>
+        <v>477281</v>
       </c>
       <c r="R71" t="n">
-        <v>6854939</v>
+        <v>6854562</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8097,12 +8084,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8117,49 +8104,49 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323126</t>
+          <t>https://artportalen.se/Sighting/133688499</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133688678</v>
+        <v>133688781</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8169,10 +8156,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477280</v>
+        <v>477266</v>
       </c>
       <c r="R72" t="n">
-        <v>6854562</v>
+        <v>6854565</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8230,54 +8217,51 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688678</t>
+          <t>https://artportalen.se/Sighting/133688781</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134530183</v>
+        <v>133688863</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477164</v>
+        <v>477250</v>
       </c>
       <c r="R73" t="n">
-        <v>6854653</v>
+        <v>6854562</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8318,76 +8302,55 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Diabas</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Diabase # stort block I kanten av lok</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134530183</t>
+          <t>https://artportalen.se/Sighting/133688863</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127323374</v>
+        <v>133688890</v>
       </c>
       <c r="B74" t="n">
-        <v>79917</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8397,10 +8360,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476940</v>
+        <v>477239</v>
       </c>
       <c r="R74" t="n">
-        <v>6854907</v>
+        <v>6854556</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8427,12 +8390,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8447,65 +8410,65 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323374</t>
+          <t>https://artportalen.se/Sighting/133688890</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127386811</v>
+        <v>133689429</v>
       </c>
       <c r="B75" t="n">
-        <v>79917</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476887</v>
+        <v>477202</v>
       </c>
       <c r="R75" t="n">
-        <v>6854810</v>
+        <v>6854583</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8529,12 +8492,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8549,68 +8512,65 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127386811</t>
+          <t>https://artportalen.se/Sighting/133689429</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134530306</v>
+        <v>133689512</v>
       </c>
       <c r="B76" t="n">
-        <v>79800</v>
+        <v>99195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>230550</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mjölig knopplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Biatora chrysantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Zahlbr.) Printzen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477164</v>
+        <v>477213</v>
       </c>
       <c r="R76" t="n">
-        <v>6854653</v>
+        <v>6854605</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8648,54 +8608,33 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Diabas</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Diabase # mossa på stort block I kanten av lok</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134530306</t>
+          <t>https://artportalen.se/Sighting/133689512</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134526048</v>
+        <v>133689901</v>
       </c>
       <c r="B77" t="n">
-        <v>76078</v>
+        <v>99195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8703,35 +8642,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>266100</v>
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Abrothallus diederichii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Suija &amp; F.Berger</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477204</v>
+        <v>477179</v>
       </c>
       <c r="R77" t="n">
-        <v>6854574</v>
+        <v>6854626</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8769,48 +8719,2755 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>lunglav</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>sälg vid lok # Lobaria pulmonaria</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689901</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133690721</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>477168</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6854646</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133690721</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133691269</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>477132</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6854710</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133691269</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134669713</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>477098</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6854401</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669713</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134914999</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>477113</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6854388</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134914999</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135650691</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>477080</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6854389</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650691</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135650762</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>477080</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6854394</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650762</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135650783</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>477074</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6854400</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650783</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135650820</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>477083</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6854402</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650820</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135651543</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>477100</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6854441</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651543</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135651644</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>477110</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6854460</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651644</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135652020</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>477104</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6854499</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652020</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135652062</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>477131</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6854518</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652062</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135652088</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>477134</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6854515</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652088</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135652139</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>477138</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6854521</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652139</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135652151</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>477131</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6854530</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652151</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135652185</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>477138</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6854534</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652185</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135652319</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>477113</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6854549</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652319</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135652423</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>477106</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6854574</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652423</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135652655</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>477032</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6854648</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652655</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127323126</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>476950</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6854939</v>
+      </c>
+      <c r="S97" t="n">
+        <v>20</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323126</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>133688678</v>
+      </c>
+      <c r="B98" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>477280</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6854562</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688678</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>134530183</v>
+      </c>
+      <c r="B99" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>477164</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6854653</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Diabas</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Diabase # stort block I kanten av lok</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530183</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127323374</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>476940</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6854907</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323374</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127386811</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>476887</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6854810</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386811</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>134530306</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79800</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>230550</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mjölig knopplav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Biatora chrysantha</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Zahlbr.) Printzen</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Sjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>477164</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6854653</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Diabas</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Diabase # mossa på stort block I kanten av lok</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530306</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>134526048</v>
+      </c>
+      <c r="B103" t="n">
+        <v>76078</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>266100</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Abrothallus diederichii</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Suija &amp; F.Berger</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Sjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>477204</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6854574</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>sälg vid lok # Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134526048</t>
         </is>
@@ -8894,6 +11551,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -3368,7 +3368,7 @@
         <v>135651460</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>135651610</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>135651722</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>135652158</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>135651380</v>
       </c>
       <c r="B34" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>135651365</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135652113</v>
       </c>
       <c r="B48" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>135652154</v>
       </c>
       <c r="B49" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>135650691</v>
       </c>
       <c r="B82" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>135650762</v>
       </c>
       <c r="B83" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>135650783</v>
       </c>
       <c r="B84" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>135650820</v>
       </c>
       <c r="B85" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>135651543</v>
       </c>
       <c r="B86" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>135651644</v>
       </c>
       <c r="B87" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>135652020</v>
       </c>
       <c r="B88" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>135652062</v>
       </c>
       <c r="B89" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>135652088</v>
       </c>
       <c r="B90" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>135652139</v>
       </c>
       <c r="B91" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>135652151</v>
       </c>
       <c r="B92" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>135652185</v>
       </c>
       <c r="B93" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>135652319</v>
       </c>
       <c r="B94" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>135652423</v>
       </c>
       <c r="B95" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>135652655</v>
       </c>
       <c r="B96" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ77"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3365,51 +3365,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134530339</v>
+        <v>135651460</v>
       </c>
       <c r="B27" t="n">
-        <v>75468</v>
+        <v>79441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477164</v>
+        <v>477124</v>
       </c>
       <c r="R27" t="n">
-        <v>6854653</v>
+        <v>6854444</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3433,12 +3430,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,100 +3444,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>i kanten av lok # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134530339</t>
+          <t>https://artportalen.se/Sighting/135651460</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134525785</v>
+        <v>135651610</v>
       </c>
       <c r="B28" t="n">
-        <v>75340</v>
+        <v>79441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477229</v>
+        <v>477101</v>
       </c>
       <c r="R28" t="n">
-        <v>6854414</v>
+        <v>6854442</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3564,12 +3532,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,81 +3546,55 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134525785</t>
+          <t>https://artportalen.se/Sighting/135651610</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127323353</v>
+        <v>135651722</v>
       </c>
       <c r="B29" t="n">
-        <v>78730</v>
+        <v>79441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3662,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476938</v>
+        <v>477110</v>
       </c>
       <c r="R29" t="n">
-        <v>6854905</v>
+        <v>6854461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3692,12 +3634,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,49 +3654,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323353</t>
+          <t>https://artportalen.se/Sighting/135651722</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127323284</v>
+        <v>135652158</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>79441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3764,13 +3706,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476946</v>
+        <v>477131</v>
       </c>
       <c r="R30" t="n">
-        <v>6854917</v>
+        <v>6854528</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3794,12 +3736,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3814,27 +3756,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323284</t>
+          <t>https://artportalen.se/Sighting/135652158</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133686261</v>
+        <v>134530339</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>75468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,37 +3784,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477266</v>
+        <v>477164</v>
       </c>
       <c r="R31" t="n">
-        <v>6854496</v>
+        <v>6854653</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3910,71 +3855,100 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>i kanten av lok # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133686261</t>
+          <t>https://artportalen.se/Sighting/134530339</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127323834</v>
+        <v>134525785</v>
       </c>
       <c r="B32" t="n">
-        <v>80432</v>
+        <v>75340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477019</v>
+        <v>477229</v>
       </c>
       <c r="R32" t="n">
-        <v>6854759</v>
+        <v>6854414</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3998,12 +3972,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,33 +3986,59 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323834</t>
+          <t>https://artportalen.se/Sighting/134525785</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127323921</v>
+        <v>127323353</v>
       </c>
       <c r="B33" t="n">
-        <v>80432</v>
+        <v>78730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477064</v>
+        <v>476938</v>
       </c>
       <c r="R33" t="n">
-        <v>6854729</v>
+        <v>6854905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,16 +4131,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323921</t>
+          <t>https://artportalen.se/Sighting/127323353</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127323931</v>
+        <v>135651380</v>
       </c>
       <c r="B34" t="n">
-        <v>80432</v>
+        <v>79198</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,34 +4148,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477063</v>
+        <v>477131</v>
       </c>
       <c r="R34" t="n">
-        <v>6854712</v>
+        <v>6854439</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4222,27 +4222,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323931</t>
+          <t>https://artportalen.se/Sighting/135651380</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127323933</v>
+        <v>127323284</v>
       </c>
       <c r="B35" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477031</v>
+        <v>476946</v>
       </c>
       <c r="R35" t="n">
-        <v>6854762</v>
+        <v>6854917</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4324,27 +4324,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323933</t>
+          <t>https://artportalen.se/Sighting/127323284</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133684870</v>
+        <v>133686261</v>
       </c>
       <c r="B36" t="n">
-        <v>80488</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4352,37 +4352,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477230</v>
+        <v>477266</v>
       </c>
       <c r="R36" t="n">
-        <v>6854415</v>
+        <v>6854496</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4426,27 +4426,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133684870</t>
+          <t>https://artportalen.se/Sighting/133686261</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133685839</v>
+        <v>135651365</v>
       </c>
       <c r="B37" t="n">
-        <v>80488</v>
+        <v>80060</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,34 +4454,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477222</v>
+        <v>477137</v>
       </c>
       <c r="R37" t="n">
-        <v>6854404</v>
+        <v>6854442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4539,16 +4539,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685839</t>
+          <t>https://artportalen.se/Sighting/135651365</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133688661</v>
+        <v>127323834</v>
       </c>
       <c r="B38" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477281</v>
+        <v>477019</v>
       </c>
       <c r="R38" t="n">
-        <v>6854562</v>
+        <v>6854759</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,17 +4610,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4635,27 +4630,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688661</t>
+          <t>https://artportalen.se/Sighting/127323834</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133689273</v>
+        <v>127323921</v>
       </c>
       <c r="B39" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4687,10 +4682,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477171</v>
+        <v>477064</v>
       </c>
       <c r="R39" t="n">
-        <v>6854572</v>
+        <v>6854729</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,12 +4712,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,27 +4732,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689273</t>
+          <t>https://artportalen.se/Sighting/127323921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133689338</v>
+        <v>127323931</v>
       </c>
       <c r="B40" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477202</v>
+        <v>477063</v>
       </c>
       <c r="R40" t="n">
-        <v>6854583</v>
+        <v>6854712</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4819,12 +4814,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4839,27 +4834,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689338</t>
+          <t>https://artportalen.se/Sighting/127323931</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134526038</v>
+        <v>127323933</v>
       </c>
       <c r="B41" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4885,22 +4880,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477204</v>
+        <v>477031</v>
       </c>
       <c r="R41" t="n">
-        <v>6854574</v>
+        <v>6854762</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4924,12 +4916,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4938,81 +4930,55 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>vid lok # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134526038</t>
+          <t>https://artportalen.se/Sighting/127323933</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127324159</v>
+        <v>133684870</v>
       </c>
       <c r="B42" t="n">
-        <v>80460</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5022,13 +4988,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477033</v>
+        <v>477230</v>
       </c>
       <c r="R42" t="n">
-        <v>6854650</v>
+        <v>6854415</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5052,12 +5018,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5083,57 +5049,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324159</t>
+          <t>https://artportalen.se/Sighting/133684870</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134525868</v>
+        <v>133685839</v>
       </c>
       <c r="B43" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477321</v>
+        <v>477222</v>
       </c>
       <c r="R43" t="n">
-        <v>6854556</v>
+        <v>6854404</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5171,44 +5134,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134525868</t>
+          <t>https://artportalen.se/Sighting/133685839</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127324353</v>
+        <v>133688661</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5216,37 +5168,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477164</v>
+        <v>477281</v>
       </c>
       <c r="R44" t="n">
-        <v>6854349</v>
+        <v>6854562</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5270,12 +5222,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,38 +5258,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324353</t>
+          <t>https://artportalen.se/Sighting/133688661</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127323728</v>
+        <v>133689273</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5342,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476992</v>
+        <v>477171</v>
       </c>
       <c r="R45" t="n">
-        <v>6854784</v>
+        <v>6854572</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,12 +5329,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5392,71 +5349,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323728</t>
+          <t>https://artportalen.se/Sighting/133689273</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127323767</v>
+        <v>133689338</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476962</v>
+        <v>477202</v>
       </c>
       <c r="R46" t="n">
-        <v>6854787</v>
+        <v>6854583</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5483,12 +5431,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5514,54 +5462,57 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323767</t>
+          <t>https://artportalen.se/Sighting/133689338</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127323861</v>
+        <v>134526038</v>
       </c>
       <c r="B47" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476993</v>
+        <v>477204</v>
       </c>
       <c r="R47" t="n">
-        <v>6854793</v>
+        <v>6854574</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5585,12 +5536,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5599,55 +5550,81 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>vid lok # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323861</t>
+          <t>https://artportalen.se/Sighting/134526038</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127323877</v>
+        <v>135652113</v>
       </c>
       <c r="B48" t="n">
-        <v>99118</v>
+        <v>80556</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,13 +5634,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476997</v>
+        <v>477139</v>
       </c>
       <c r="R48" t="n">
-        <v>6854787</v>
+        <v>6854519</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5687,12 +5664,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,68 +5695,54 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323877</t>
+          <t>https://artportalen.se/Sighting/135652113</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127323884</v>
+        <v>135652154</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>80556</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477019</v>
+        <v>477131</v>
       </c>
       <c r="R49" t="n">
-        <v>6854759</v>
+        <v>6854528</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5803,17 +5766,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ljusa blad. Kantzonseffekt vid väg.</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,49 +5786,49 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323884</t>
+          <t>https://artportalen.se/Sighting/135652154</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127323904</v>
+        <v>127324159</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>80460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5880,10 +5838,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477003</v>
+        <v>477033</v>
       </c>
       <c r="R50" t="n">
-        <v>6854772</v>
+        <v>6854650</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5941,54 +5899,57 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323904</t>
+          <t>https://artportalen.se/Sighting/127324159</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127323912</v>
+        <v>134525868</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>80492</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Sjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477010</v>
+        <v>477321</v>
       </c>
       <c r="R51" t="n">
-        <v>6854772</v>
+        <v>6854556</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6012,12 +5973,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,71 +5987,82 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Janolof Hermansson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323912</t>
+          <t>https://artportalen.se/Sighting/134525868</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127323923</v>
+        <v>127324353</v>
       </c>
       <c r="B52" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477014</v>
+        <v>477164</v>
       </c>
       <c r="R52" t="n">
-        <v>6854772</v>
+        <v>6854349</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6145,54 +6117,54 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323923</t>
+          <t>https://artportalen.se/Sighting/127324353</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127323993</v>
+        <v>135652838</v>
       </c>
       <c r="B53" t="n">
-        <v>99118</v>
+        <v>41610</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>215713</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477076</v>
+        <v>477139</v>
       </c>
       <c r="R53" t="n">
-        <v>6854706</v>
+        <v>6854377</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6216,12 +6188,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6236,65 +6213,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323993</t>
+          <t>https://artportalen.se/Sighting/135652838</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127324058</v>
+        <v>135653121</v>
       </c>
       <c r="B54" t="n">
-        <v>99118</v>
+        <v>42875</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>216248</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Baltiskt skogsfly</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Xestia baltica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Valle, 1940)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477039</v>
+        <v>477097</v>
       </c>
       <c r="R54" t="n">
-        <v>6854676</v>
+        <v>6854375</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6318,12 +6295,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,54 +6326,54 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324058</t>
+          <t>https://artportalen.se/Sighting/135653121</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127324130</v>
+        <v>135653167</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>42870</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>216255</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödfläckigt jordfly</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Xestia alpicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Zetterstedt, 1839)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Flärken, Flärken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477037</v>
+        <v>477098</v>
       </c>
       <c r="R55" t="n">
-        <v>6854645</v>
+        <v>6854370</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,12 +6397,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6451,16 +6428,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127324130</t>
+          <t>https://artportalen.se/Sighting/135653167</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133685659</v>
+        <v>127323728</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,10 +6469,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477222</v>
+        <v>476992</v>
       </c>
       <c r="R56" t="n">
-        <v>6854402</v>
+        <v>6854784</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6522,12 +6499,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6542,27 +6519,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685659</t>
+          <t>https://artportalen.se/Sighting/127323728</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133685747</v>
+        <v>127323767</v>
       </c>
       <c r="B57" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6589,7 +6566,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6603,10 +6580,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477222</v>
+        <v>476962</v>
       </c>
       <c r="R57" t="n">
-        <v>6854404</v>
+        <v>6854787</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6633,12 +6610,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6664,16 +6641,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685747</t>
+          <t>https://artportalen.se/Sighting/127323767</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133685866</v>
+        <v>127323861</v>
       </c>
       <c r="B58" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6701,17 +6678,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477215</v>
+        <v>476993</v>
       </c>
       <c r="R58" t="n">
-        <v>6854428</v>
+        <v>6854793</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6735,12 +6712,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6766,16 +6743,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685866</t>
+          <t>https://artportalen.se/Sighting/127323861</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133685908</v>
+        <v>127323877</v>
       </c>
       <c r="B59" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6800,29 +6777,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477218</v>
+        <v>476997</v>
       </c>
       <c r="R59" t="n">
-        <v>6854443</v>
+        <v>6854787</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6846,12 +6814,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6877,16 +6845,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133685908</t>
+          <t>https://artportalen.se/Sighting/127323877</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133688499</v>
+        <v>127323884</v>
       </c>
       <c r="B60" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6913,7 +6881,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6921,19 +6889,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477281</v>
+        <v>477019</v>
       </c>
       <c r="R60" t="n">
-        <v>6854562</v>
+        <v>6854759</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6957,12 +6930,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ljusa blad. Kantzonseffekt vid väg.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,27 +6955,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688499</t>
+          <t>https://artportalen.se/Sighting/127323884</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133688781</v>
+        <v>127323904</v>
       </c>
       <c r="B61" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7029,13 +7007,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477266</v>
+        <v>477003</v>
       </c>
       <c r="R61" t="n">
-        <v>6854565</v>
+        <v>6854772</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7059,12 +7037,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7090,16 +7068,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688781</t>
+          <t>https://artportalen.se/Sighting/127323904</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133688863</v>
+        <v>127323912</v>
       </c>
       <c r="B62" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7131,13 +7109,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477250</v>
+        <v>477010</v>
       </c>
       <c r="R62" t="n">
-        <v>6854562</v>
+        <v>6854772</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7161,12 +7139,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7192,16 +7170,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688863</t>
+          <t>https://artportalen.se/Sighting/127323912</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133688890</v>
+        <v>127323923</v>
       </c>
       <c r="B63" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7233,10 +7211,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477239</v>
+        <v>477014</v>
       </c>
       <c r="R63" t="n">
-        <v>6854556</v>
+        <v>6854772</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7263,12 +7241,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7294,16 +7272,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688890</t>
+          <t>https://artportalen.se/Sighting/127323923</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133689429</v>
+        <v>127323993</v>
       </c>
       <c r="B64" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7335,13 +7313,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477202</v>
+        <v>477076</v>
       </c>
       <c r="R64" t="n">
-        <v>6854583</v>
+        <v>6854706</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7365,12 +7343,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7385,27 +7363,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689429</t>
+          <t>https://artportalen.se/Sighting/127323993</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133689512</v>
+        <v>127324058</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7433,17 +7411,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477213</v>
+        <v>477039</v>
       </c>
       <c r="R65" t="n">
-        <v>6854605</v>
+        <v>6854676</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7467,12 +7445,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7498,16 +7476,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689512</t>
+          <t>https://artportalen.se/Sighting/127324058</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133689901</v>
+        <v>127324130</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7532,29 +7510,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477179</v>
+        <v>477037</v>
       </c>
       <c r="R66" t="n">
-        <v>6854626</v>
+        <v>6854645</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7578,12 +7547,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7609,13 +7578,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133689901</t>
+          <t>https://artportalen.se/Sighting/127324130</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133690721</v>
+        <v>133685659</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -7650,10 +7619,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477168</v>
+        <v>477222</v>
       </c>
       <c r="R67" t="n">
-        <v>6854646</v>
+        <v>6854402</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7711,13 +7680,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133690721</t>
+          <t>https://artportalen.se/Sighting/133685659</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133691269</v>
+        <v>133685747</v>
       </c>
       <c r="B68" t="n">
         <v>99195</v>
@@ -7745,17 +7714,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477132</v>
+        <v>477222</v>
       </c>
       <c r="R68" t="n">
-        <v>6854710</v>
+        <v>6854404</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7813,13 +7791,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133691269</t>
+          <t>https://artportalen.se/Sighting/133685747</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134669713</v>
+        <v>133685866</v>
       </c>
       <c r="B69" t="n">
         <v>99195</v>
@@ -7854,10 +7832,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477098</v>
+        <v>477215</v>
       </c>
       <c r="R69" t="n">
-        <v>6854401</v>
+        <v>6854428</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7884,12 +7862,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7915,16 +7893,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134669713</t>
+          <t>https://artportalen.se/Sighting/133685866</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134914999</v>
+        <v>133685908</v>
       </c>
       <c r="B70" t="n">
-        <v>99242</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7951,7 +7929,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7965,10 +7943,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477113</v>
+        <v>477218</v>
       </c>
       <c r="R70" t="n">
-        <v>6854388</v>
+        <v>6854443</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7995,12 +7973,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8026,54 +8004,63 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134914999</t>
+          <t>https://artportalen.se/Sighting/133685908</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127323126</v>
+        <v>133688499</v>
       </c>
       <c r="B71" t="n">
-        <v>79085</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476950</v>
+        <v>477281</v>
       </c>
       <c r="R71" t="n">
-        <v>6854939</v>
+        <v>6854562</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8097,12 +8084,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8117,49 +8104,49 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323126</t>
+          <t>https://artportalen.se/Sighting/133688499</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133688678</v>
+        <v>133688781</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8169,10 +8156,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477280</v>
+        <v>477266</v>
       </c>
       <c r="R72" t="n">
-        <v>6854562</v>
+        <v>6854565</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8230,54 +8217,51 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133688678</t>
+          <t>https://artportalen.se/Sighting/133688781</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134530183</v>
+        <v>133688863</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477164</v>
+        <v>477250</v>
       </c>
       <c r="R73" t="n">
-        <v>6854653</v>
+        <v>6854562</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8318,76 +8302,55 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Diabas</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Diabase # stort block I kanten av lok</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134530183</t>
+          <t>https://artportalen.se/Sighting/133688863</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127323374</v>
+        <v>133688890</v>
       </c>
       <c r="B74" t="n">
-        <v>79917</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8397,10 +8360,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476940</v>
+        <v>477239</v>
       </c>
       <c r="R74" t="n">
-        <v>6854907</v>
+        <v>6854556</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8427,12 +8390,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8447,65 +8410,65 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323374</t>
+          <t>https://artportalen.se/Sighting/133688890</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127386811</v>
+        <v>133689429</v>
       </c>
       <c r="B75" t="n">
-        <v>79917</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476887</v>
+        <v>477202</v>
       </c>
       <c r="R75" t="n">
-        <v>6854810</v>
+        <v>6854583</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8529,12 +8492,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8549,68 +8512,65 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127386811</t>
+          <t>https://artportalen.se/Sighting/133689429</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134530306</v>
+        <v>133689512</v>
       </c>
       <c r="B76" t="n">
-        <v>79800</v>
+        <v>99195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>230550</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mjölig knopplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Biatora chrysantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Zahlbr.) Printzen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477164</v>
+        <v>477213</v>
       </c>
       <c r="R76" t="n">
-        <v>6854653</v>
+        <v>6854605</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8648,54 +8608,33 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Diabas</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Diabase # mossa på stort block I kanten av lok</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134530306</t>
+          <t>https://artportalen.se/Sighting/133689512</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134526048</v>
+        <v>133689901</v>
       </c>
       <c r="B77" t="n">
-        <v>76078</v>
+        <v>99195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8703,35 +8642,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>266100</v>
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Abrothallus diederichii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Suija &amp; F.Berger</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sjöberget, Hjd</t>
+          <t>Flärken, Flärken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477204</v>
+        <v>477179</v>
       </c>
       <c r="R77" t="n">
-        <v>6854574</v>
+        <v>6854626</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8769,48 +8719,2857 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>lunglav</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>sälg vid lok # Lobaria pulmonaria</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689901</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133690721</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>477168</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6854646</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133690721</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133691269</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>477132</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6854710</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133691269</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134669713</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>477098</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6854401</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669713</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134914999</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>477113</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6854388</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134914999</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135650691</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>477080</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6854389</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650691</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135650762</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>477080</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6854394</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650762</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135650783</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>477074</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6854400</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650783</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135650820</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>477083</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6854402</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650820</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135651543</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>477100</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6854441</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651543</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135651644</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>477110</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6854460</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651644</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135652020</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>477104</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6854499</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652020</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135652062</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>477131</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6854518</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652062</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135652088</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>477134</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6854515</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652088</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135652139</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>477138</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6854521</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652139</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135652151</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>477131</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6854530</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652151</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135652185</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>477138</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6854534</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652185</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135652319</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>477113</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6854549</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652319</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135652423</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>477106</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6854574</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652423</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135652655</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>477032</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6854648</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135652655</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135894352</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Mörtviken, Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>477136</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6854355</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135894352</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127323126</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>476950</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6854939</v>
+      </c>
+      <c r="S98" t="n">
+        <v>20</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323126</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>133688678</v>
+      </c>
+      <c r="B99" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>477280</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6854562</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688678</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>134530183</v>
+      </c>
+      <c r="B100" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Sjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>477164</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6854653</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Diabas</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Diabase # stort block I kanten av lok</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530183</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127323374</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Flärken, Flärken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>476940</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6854907</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323374</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127386811</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Mörtviken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>476887</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6854810</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386811</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>134530306</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79800</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>230550</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mjölig knopplav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Biatora chrysantha</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Zahlbr.) Printzen</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Sjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>477164</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6854653</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Diabas</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Diabase # mossa på stort block I kanten av lok</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530306</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>134526048</v>
+      </c>
+      <c r="B104" t="n">
+        <v>76078</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>266100</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Abrothallus diederichii</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Suija &amp; F.Berger</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Sjöberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>477204</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6854574</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>sälg vid lok # Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134526048</t>
         </is>
@@ -8894,6 +11653,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -9162,7 +9162,7 @@
         <v>135650691</v>
       </c>
       <c r="B82" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>135650762</v>
       </c>
       <c r="B83" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>135650783</v>
       </c>
       <c r="B84" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>135650820</v>
       </c>
       <c r="B85" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>135651543</v>
       </c>
       <c r="B86" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>135651644</v>
       </c>
       <c r="B87" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>135652020</v>
       </c>
       <c r="B88" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>135652062</v>
       </c>
       <c r="B89" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>135652088</v>
       </c>
       <c r="B90" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>135652139</v>
       </c>
       <c r="B91" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>135652151</v>
       </c>
       <c r="B92" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>135652185</v>
       </c>
       <c r="B93" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>135652319</v>
       </c>
       <c r="B94" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>135652423</v>
       </c>
       <c r="B95" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>135652655</v>
       </c>
       <c r="B96" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>135894352</v>
       </c>
       <c r="B97" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97737</v>
+        <v>97754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905515</v>
       </c>
       <c r="B52" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905525</v>
       </c>
       <c r="B53" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905526</v>
       </c>
       <c r="B54" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905531</v>
       </c>
       <c r="B55" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905533</v>
       </c>
       <c r="B56" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905543</v>
       </c>
       <c r="B57" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905551</v>
       </c>
       <c r="B58" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905564</v>
       </c>
       <c r="B59" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905573</v>
       </c>
       <c r="B60" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905574</v>
       </c>
       <c r="B61" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905579</v>
       </c>
       <c r="B62" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905584</v>
       </c>
       <c r="B63" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905588</v>
       </c>
       <c r="B64" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905612</v>
       </c>
       <c r="B65" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>135905617</v>
       </c>
       <c r="B68" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>135891979</v>
       </c>
       <c r="B69" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>135891978</v>
       </c>
       <c r="B73" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135891989</v>
       </c>
       <c r="B74" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>135892005</v>
       </c>
       <c r="B75" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135892070</v>
       </c>
       <c r="B76" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135892080</v>
       </c>
       <c r="B77" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>135891990</v>
       </c>
       <c r="B78" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>135892082</v>
       </c>
       <c r="B79" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>135892108</v>
       </c>
       <c r="B83" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>135892114</v>
       </c>
       <c r="B84" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>135892077</v>
       </c>
       <c r="B89" t="n">
-        <v>92511</v>
+        <v>92525</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>135651460</v>
       </c>
       <c r="B92" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>135651610</v>
       </c>
       <c r="B93" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>135651722</v>
       </c>
       <c r="B94" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>135652158</v>
       </c>
       <c r="B95" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135892088</v>
       </c>
       <c r="B96" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>135892091</v>
       </c>
       <c r="B97" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>135892097</v>
       </c>
       <c r="B98" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>135892109</v>
       </c>
       <c r="B99" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>135891997</v>
       </c>
       <c r="B103" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>135892020</v>
       </c>
       <c r="B104" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>135892026</v>
       </c>
       <c r="B105" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>135892069</v>
       </c>
       <c r="B106" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>135892083</v>
       </c>
       <c r="B107" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>135892113</v>
       </c>
       <c r="B108" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>135651380</v>
       </c>
       <c r="B109" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>135892007</v>
       </c>
       <c r="B110" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>135892018</v>
       </c>
       <c r="B111" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>135892021</v>
       </c>
       <c r="B112" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>135892032</v>
       </c>
       <c r="B113" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>135892046</v>
       </c>
       <c r="B114" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>135892071</v>
       </c>
       <c r="B115" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>135892100</v>
       </c>
       <c r="B116" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>135905510</v>
       </c>
       <c r="B117" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>135905516</v>
       </c>
       <c r="B118" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>135905536</v>
       </c>
       <c r="B119" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>135905538</v>
       </c>
       <c r="B120" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>135905541</v>
       </c>
       <c r="B121" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>135905546</v>
       </c>
       <c r="B122" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>135905554</v>
       </c>
       <c r="B123" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>135905562</v>
       </c>
       <c r="B124" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>135905567</v>
       </c>
       <c r="B125" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135905572</v>
       </c>
       <c r="B126" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135905576</v>
       </c>
       <c r="B127" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>135892068</v>
       </c>
       <c r="B128" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>135892085</v>
       </c>
       <c r="B129" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>135892111</v>
       </c>
       <c r="B130" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>135905563</v>
       </c>
       <c r="B131" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>135651365</v>
       </c>
       <c r="B134" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>135891992</v>
       </c>
       <c r="B135" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>135891995</v>
       </c>
       <c r="B136" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>135892002</v>
       </c>
       <c r="B137" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>135892004</v>
       </c>
       <c r="B138" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>135892008</v>
       </c>
       <c r="B139" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>135892012</v>
       </c>
       <c r="B140" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>135892017</v>
       </c>
       <c r="B141" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>135892025</v>
       </c>
       <c r="B142" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>135892027</v>
       </c>
       <c r="B143" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>135892028</v>
       </c>
       <c r="B144" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>135892038</v>
       </c>
       <c r="B145" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>135892040</v>
       </c>
       <c r="B146" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>135892043</v>
       </c>
       <c r="B147" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>135892047</v>
       </c>
       <c r="B148" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>135892052</v>
       </c>
       <c r="B149" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>135892054</v>
       </c>
       <c r="B150" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135892055</v>
       </c>
       <c r="B151" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135892058</v>
       </c>
       <c r="B152" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>135892059</v>
       </c>
       <c r="B153" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>135892062</v>
       </c>
       <c r="B154" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>135892065</v>
       </c>
       <c r="B155" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>135892074</v>
       </c>
       <c r="B156" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>135892075</v>
       </c>
       <c r="B157" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>135892078</v>
       </c>
       <c r="B158" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>135905512</v>
       </c>
       <c r="B159" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>135905520</v>
       </c>
       <c r="B160" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>135905528</v>
       </c>
       <c r="B161" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>135905535</v>
       </c>
       <c r="B162" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>135905540</v>
       </c>
       <c r="B163" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>135905548</v>
       </c>
       <c r="B164" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>135905550</v>
       </c>
       <c r="B165" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>135905557</v>
       </c>
       <c r="B166" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>135905569</v>
       </c>
       <c r="B167" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>135905571</v>
       </c>
       <c r="B168" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>135905581</v>
       </c>
       <c r="B169" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>135905583</v>
       </c>
       <c r="B170" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>135905586</v>
       </c>
       <c r="B171" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>135652113</v>
       </c>
       <c r="B182" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>135652154</v>
       </c>
       <c r="B183" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>135892093</v>
       </c>
       <c r="B184" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>135892096</v>
       </c>
       <c r="B185" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>135892103</v>
       </c>
       <c r="B186" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>135892105</v>
       </c>
       <c r="B187" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>135905587</v>
       </c>
       <c r="B188" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>135905595</v>
       </c>
       <c r="B189" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>135905596</v>
       </c>
       <c r="B190" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>135905604</v>
       </c>
       <c r="B191" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>135905609</v>
       </c>
       <c r="B192" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>135892106</v>
       </c>
       <c r="B195" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>135905611</v>
       </c>
       <c r="B196" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>135905530</v>
       </c>
       <c r="B197" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>135652838</v>
       </c>
       <c r="B199" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>135653121</v>
       </c>
       <c r="B200" t="n">
-        <v>42875</v>
+        <v>42877</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>135653167</v>
       </c>
       <c r="B201" t="n">
-        <v>42870</v>
+        <v>42872</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>135650691</v>
       </c>
       <c r="B228" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>135650762</v>
       </c>
       <c r="B229" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>135650783</v>
       </c>
       <c r="B230" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>135650820</v>
       </c>
       <c r="B231" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>135651543</v>
       </c>
       <c r="B232" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>135651644</v>
       </c>
       <c r="B233" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>135652020</v>
       </c>
       <c r="B234" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>135652062</v>
       </c>
       <c r="B235" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>135652088</v>
       </c>
       <c r="B236" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>135652139</v>
       </c>
       <c r="B237" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>135652151</v>
       </c>
       <c r="B238" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>135652185</v>
       </c>
       <c r="B239" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>135652319</v>
       </c>
       <c r="B240" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>135652423</v>
       </c>
       <c r="B241" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>135652655</v>
       </c>
       <c r="B242" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>135892050</v>
       </c>
       <c r="B243" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>135892090</v>
       </c>
       <c r="B244" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>135892104</v>
       </c>
       <c r="B245" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>135892110</v>
       </c>
       <c r="B246" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>135892112</v>
       </c>
       <c r="B247" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>135894352</v>
       </c>
       <c r="B248" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>135905524</v>
       </c>
       <c r="B249" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>135905532</v>
       </c>
       <c r="B250" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>135905542</v>
       </c>
       <c r="B251" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>135905549</v>
       </c>
       <c r="B252" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>135905558</v>
       </c>
       <c r="B253" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>135905577</v>
       </c>
       <c r="B254" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>135905580</v>
       </c>
       <c r="B255" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>135905582</v>
       </c>
       <c r="B256" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>135905589</v>
       </c>
       <c r="B257" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>135905591</v>
       </c>
       <c r="B258" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>135905592</v>
       </c>
       <c r="B259" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>135905598</v>
       </c>
       <c r="B260" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>135905599</v>
       </c>
       <c r="B261" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>135905601</v>
       </c>
       <c r="B262" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>135905602</v>
       </c>
       <c r="B263" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>135905605</v>
       </c>
       <c r="B264" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>135905606</v>
       </c>
       <c r="B265" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>135905608</v>
       </c>
       <c r="B266" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>135905614</v>
       </c>
       <c r="B267" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>135905517</v>
       </c>
       <c r="B268" t="n">
-        <v>103992</v>
+        <v>104012</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>135892006</v>
       </c>
       <c r="B270" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>135892015</v>
       </c>
       <c r="B271" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>135892044</v>
       </c>
       <c r="B272" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135892072</v>
       </c>
       <c r="B273" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>135905509</v>
       </c>
       <c r="B274" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>135905514</v>
       </c>
       <c r="B275" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>135905521</v>
       </c>
       <c r="B276" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>135905527</v>
       </c>
       <c r="B277" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>135905534</v>
       </c>
       <c r="B278" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>135905539</v>
       </c>
       <c r="B279" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>135905544</v>
       </c>
       <c r="B280" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>135905545</v>
       </c>
       <c r="B281" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>135905552</v>
       </c>
       <c r="B282" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>135905556</v>
       </c>
       <c r="B283" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>135905561</v>
       </c>
       <c r="B284" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>135905566</v>
       </c>
       <c r="B285" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>135905570</v>
       </c>
       <c r="B286" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>135905575</v>
       </c>
       <c r="B287" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>135905578</v>
       </c>
       <c r="B288" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>135905615</v>
       </c>
       <c r="B289" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>135892019</v>
       </c>
       <c r="B294" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>135892053</v>
       </c>
       <c r="B295" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>135892084</v>
       </c>
       <c r="B296" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>135905568</v>
       </c>
       <c r="B297" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97754</v>
+        <v>97755</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92650</v>
+        <v>92651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92525</v>
+        <v>92526</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>135651460</v>
       </c>
       <c r="B101" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>135651610</v>
       </c>
       <c r="B102" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>135651722</v>
       </c>
       <c r="B103" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>135652158</v>
       </c>
       <c r="B104" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>135651380</v>
       </c>
       <c r="B118" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>135651365</v>
       </c>
       <c r="B148" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>135652113</v>
       </c>
       <c r="B197" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>135652154</v>
       </c>
       <c r="B198" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>135650691</v>
       </c>
       <c r="B247" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>135650762</v>
       </c>
       <c r="B248" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>135650783</v>
       </c>
       <c r="B249" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>135650820</v>
       </c>
       <c r="B250" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>135651543</v>
       </c>
       <c r="B251" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>135651644</v>
       </c>
       <c r="B252" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>135652020</v>
       </c>
       <c r="B253" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>135652062</v>
       </c>
       <c r="B254" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>135652088</v>
       </c>
       <c r="B255" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>135652139</v>
       </c>
       <c r="B256" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>135652151</v>
       </c>
       <c r="B257" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>135652185</v>
       </c>
       <c r="B258" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>135652319</v>
       </c>
       <c r="B259" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>135652423</v>
       </c>
       <c r="B260" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>135652655</v>
       </c>
       <c r="B261" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104012</v>
+        <v>104014</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -18789,7 +18789,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Tilde Carlinger, Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97755</v>
+        <v>97756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92526</v>
+        <v>92527</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>135650691</v>
       </c>
       <c r="B247" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>135650762</v>
       </c>
       <c r="B248" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>135650783</v>
       </c>
       <c r="B249" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>135650820</v>
       </c>
       <c r="B250" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>135651543</v>
       </c>
       <c r="B251" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>135651644</v>
       </c>
       <c r="B252" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>135652020</v>
       </c>
       <c r="B253" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>135652062</v>
       </c>
       <c r="B254" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>135652088</v>
       </c>
       <c r="B255" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>135652139</v>
       </c>
       <c r="B256" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>135652151</v>
       </c>
       <c r="B257" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>135652185</v>
       </c>
       <c r="B258" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>135652319</v>
       </c>
       <c r="B259" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>135652423</v>
       </c>
       <c r="B260" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>135652655</v>
       </c>
       <c r="B261" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97756</v>
+        <v>97757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>135651460</v>
       </c>
       <c r="B101" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>135651610</v>
       </c>
       <c r="B102" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>135651722</v>
       </c>
       <c r="B103" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>135652158</v>
       </c>
       <c r="B104" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>135651380</v>
       </c>
       <c r="B118" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>135651365</v>
       </c>
       <c r="B148" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>135652113</v>
       </c>
       <c r="B197" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>135652154</v>
       </c>
       <c r="B198" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>135905530</v>
       </c>
       <c r="B214" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>135905038</v>
       </c>
       <c r="B216" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>135652838</v>
       </c>
       <c r="B217" t="n">
-        <v>41612</v>
+        <v>41613</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>135905042</v>
       </c>
       <c r="B218" t="n">
-        <v>41612</v>
+        <v>41613</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>135653121</v>
       </c>
       <c r="B219" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>135653167</v>
       </c>
       <c r="B220" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>135650691</v>
       </c>
       <c r="B247" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>135650762</v>
       </c>
       <c r="B248" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>135650783</v>
       </c>
       <c r="B249" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>135650820</v>
       </c>
       <c r="B250" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>135651543</v>
       </c>
       <c r="B251" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>135651644</v>
       </c>
       <c r="B252" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>135652020</v>
       </c>
       <c r="B253" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>135652062</v>
       </c>
       <c r="B254" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>135652088</v>
       </c>
       <c r="B255" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>135652139</v>
       </c>
       <c r="B256" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>135652151</v>
       </c>
       <c r="B257" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>135652185</v>
       </c>
       <c r="B258" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>135652319</v>
       </c>
       <c r="B259" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>135652423</v>
       </c>
       <c r="B260" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>135652655</v>
       </c>
       <c r="B261" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104015</v>
+        <v>104016</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97757</v>
+        <v>97763</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92653</v>
+        <v>92659</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92528</v>
+        <v>92534</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>135651460</v>
       </c>
       <c r="B101" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>135651610</v>
       </c>
       <c r="B102" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>135651722</v>
       </c>
       <c r="B103" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>135652158</v>
       </c>
       <c r="B104" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>135651380</v>
       </c>
       <c r="B118" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>135651365</v>
       </c>
       <c r="B148" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>135652113</v>
       </c>
       <c r="B197" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>135652154</v>
       </c>
       <c r="B198" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>135905530</v>
       </c>
       <c r="B214" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>135905038</v>
       </c>
       <c r="B216" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>135650691</v>
       </c>
       <c r="B247" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>135650762</v>
       </c>
       <c r="B248" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>135650783</v>
       </c>
       <c r="B249" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>135650820</v>
       </c>
       <c r="B250" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>135651543</v>
       </c>
       <c r="B251" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>135651644</v>
       </c>
       <c r="B252" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>135652020</v>
       </c>
       <c r="B253" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>135652062</v>
       </c>
       <c r="B254" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>135652088</v>
       </c>
       <c r="B255" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>135652139</v>
       </c>
       <c r="B256" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>135652151</v>
       </c>
       <c r="B257" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>135652185</v>
       </c>
       <c r="B258" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>135652319</v>
       </c>
       <c r="B259" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>135652423</v>
       </c>
       <c r="B260" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>135652655</v>
       </c>
       <c r="B261" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104016</v>
+        <v>104022</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97763</v>
+        <v>97764</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92534</v>
+        <v>92535</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>135905530</v>
       </c>
       <c r="B214" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>135905038</v>
       </c>
       <c r="B216" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104022</v>
+        <v>104023</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97764</v>
+        <v>97775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92660</v>
+        <v>92666</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92535</v>
+        <v>92541</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104023</v>
+        <v>104034</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97775</v>
+        <v>97788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92666</v>
+        <v>92673</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92541</v>
+        <v>92548</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79540</v>
+        <v>79546</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79540</v>
+        <v>79546</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79540</v>
+        <v>79546</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79540</v>
+        <v>79546</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>135905530</v>
       </c>
       <c r="B214" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>135905038</v>
       </c>
       <c r="B216" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>135905042</v>
       </c>
       <c r="B218" t="n">
-        <v>41613</v>
+        <v>41618</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104034</v>
+        <v>104047</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97788</v>
+        <v>97789</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92548</v>
+        <v>92549</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
@@ -20917,7 +20917,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104047</v>
+        <v>104048</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97789</v>
+        <v>97802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81442</v>
+        <v>81455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92674</v>
+        <v>92687</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92549</v>
+        <v>92562</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79546</v>
+        <v>79559</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79546</v>
+        <v>79559</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79546</v>
+        <v>79559</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79546</v>
+        <v>79559</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>135905530</v>
       </c>
       <c r="B214" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>135905038</v>
       </c>
       <c r="B216" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>135905042</v>
       </c>
       <c r="B218" t="n">
-        <v>41618</v>
+        <v>41631</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104048</v>
+        <v>104061</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Tilde Carlinger, Erik Christiansson, Karla Alfaro Gripe</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Tilde Carlinger, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -23075,7 +23075,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
@@ -30398,7 +30398,7 @@
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
@@ -30523,7 +30523,7 @@
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135892094</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>135891999</v>
       </c>
       <c r="B8" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135892000</v>
       </c>
       <c r="B9" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>135892066</v>
       </c>
       <c r="B10" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135892089</v>
       </c>
       <c r="B11" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135892099</v>
       </c>
       <c r="B12" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135892102</v>
       </c>
       <c r="B13" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>135892045</v>
       </c>
       <c r="B14" t="n">
-        <v>97802</v>
+        <v>97803</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>135891980</v>
       </c>
       <c r="B21" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>135891988</v>
       </c>
       <c r="B22" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>135891991</v>
       </c>
       <c r="B23" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135891993</v>
       </c>
       <c r="B24" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>135891994</v>
       </c>
       <c r="B25" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135891996</v>
       </c>
       <c r="B26" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>135891998</v>
       </c>
       <c r="B27" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135892001</v>
       </c>
       <c r="B28" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135892003</v>
       </c>
       <c r="B29" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>135892009</v>
       </c>
       <c r="B30" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>135892010</v>
       </c>
       <c r="B31" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>135892011</v>
       </c>
       <c r="B32" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135892022</v>
       </c>
       <c r="B33" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>135892023</v>
       </c>
       <c r="B34" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>135892024</v>
       </c>
       <c r="B35" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135892029</v>
       </c>
       <c r="B36" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>135892033</v>
       </c>
       <c r="B37" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135892034</v>
       </c>
       <c r="B38" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>135892035</v>
       </c>
       <c r="B39" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135892037</v>
       </c>
       <c r="B40" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135892039</v>
       </c>
       <c r="B41" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>135892041</v>
       </c>
       <c r="B42" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>135892042</v>
       </c>
       <c r="B43" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>135892049</v>
       </c>
       <c r="B44" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>135892051</v>
       </c>
       <c r="B45" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>135892063</v>
       </c>
       <c r="B46" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>135892064</v>
       </c>
       <c r="B47" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135892079</v>
       </c>
       <c r="B48" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>135892081</v>
       </c>
       <c r="B49" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135892086</v>
       </c>
       <c r="B50" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>135892087</v>
       </c>
       <c r="B51" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>135905515</v>
       </c>
       <c r="B54" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>135905525</v>
       </c>
       <c r="B55" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>135905526</v>
       </c>
       <c r="B56" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>135905531</v>
       </c>
       <c r="B57" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>135905533</v>
       </c>
       <c r="B58" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>135905543</v>
       </c>
       <c r="B59" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135905551</v>
       </c>
       <c r="B60" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135905564</v>
       </c>
       <c r="B61" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135905573</v>
       </c>
       <c r="B62" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>135905574</v>
       </c>
       <c r="B63" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135905579</v>
       </c>
       <c r="B64" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>135905584</v>
       </c>
       <c r="B65" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135905588</v>
       </c>
       <c r="B66" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135905617</v>
       </c>
       <c r="B70" t="n">
-        <v>81455</v>
+        <v>81456</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135905068</v>
       </c>
       <c r="B71" t="n">
-        <v>92687</v>
+        <v>92688</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8504,7 +8504,7 @@
         <v>135891979</v>
       </c>
       <c r="B72" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>135891978</v>
       </c>
       <c r="B76" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>135891989</v>
       </c>
       <c r="B77" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135892005</v>
       </c>
       <c r="B78" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>135892070</v>
       </c>
       <c r="B79" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>135892080</v>
       </c>
       <c r="B80" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>135891990</v>
       </c>
       <c r="B81" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>135892082</v>
       </c>
       <c r="B82" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>135892108</v>
       </c>
       <c r="B86" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>135892114</v>
       </c>
       <c r="B87" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135905045</v>
       </c>
       <c r="B88" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>135905063</v>
       </c>
       <c r="B89" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135905051</v>
       </c>
       <c r="B93" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>135905055</v>
       </c>
       <c r="B94" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>135905062</v>
       </c>
       <c r="B95" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>135905065</v>
       </c>
       <c r="B96" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135892077</v>
       </c>
       <c r="B98" t="n">
-        <v>92562</v>
+        <v>92563</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>135892088</v>
       </c>
       <c r="B105" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>135892091</v>
       </c>
       <c r="B106" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>135892097</v>
       </c>
       <c r="B107" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>135892109</v>
       </c>
       <c r="B108" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135891997</v>
       </c>
       <c r="B112" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135892020</v>
       </c>
       <c r="B113" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>135892026</v>
       </c>
       <c r="B114" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>135892069</v>
       </c>
       <c r="B115" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>135892083</v>
       </c>
       <c r="B116" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>135892113</v>
       </c>
       <c r="B117" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>135892007</v>
       </c>
       <c r="B119" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>135892021</v>
       </c>
       <c r="B121" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>135892032</v>
       </c>
       <c r="B122" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>135892046</v>
       </c>
       <c r="B123" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135892071</v>
       </c>
       <c r="B124" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>135892100</v>
       </c>
       <c r="B125" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>135905039</v>
       </c>
       <c r="B126" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>135905041</v>
       </c>
       <c r="B127" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>135905046</v>
       </c>
       <c r="B128" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>135905052</v>
       </c>
       <c r="B129" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>135905059</v>
       </c>
       <c r="B130" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>135905510</v>
       </c>
       <c r="B131" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>135905516</v>
       </c>
       <c r="B132" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>135905536</v>
       </c>
       <c r="B133" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>135905538</v>
       </c>
       <c r="B134" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>135905541</v>
       </c>
       <c r="B135" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>135905546</v>
       </c>
       <c r="B136" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>135905554</v>
       </c>
       <c r="B137" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135905562</v>
       </c>
       <c r="B138" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>135905567</v>
       </c>
       <c r="B139" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>135905572</v>
       </c>
       <c r="B140" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>135905576</v>
       </c>
       <c r="B141" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>135892068</v>
       </c>
       <c r="B142" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>135892085</v>
       </c>
       <c r="B143" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>135892111</v>
       </c>
       <c r="B144" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>135905563</v>
       </c>
       <c r="B145" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>135891992</v>
       </c>
       <c r="B149" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>135891995</v>
       </c>
       <c r="B150" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>135892002</v>
       </c>
       <c r="B151" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>135892004</v>
       </c>
       <c r="B152" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>135892008</v>
       </c>
       <c r="B153" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>135892012</v>
       </c>
       <c r="B154" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>135892017</v>
       </c>
       <c r="B155" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>135892025</v>
       </c>
       <c r="B156" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>135892027</v>
       </c>
       <c r="B157" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>135892028</v>
       </c>
       <c r="B158" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135892038</v>
       </c>
       <c r="B159" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>135892040</v>
       </c>
       <c r="B160" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>135892043</v>
       </c>
       <c r="B161" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>135892047</v>
       </c>
       <c r="B162" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>135892052</v>
       </c>
       <c r="B163" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>135892054</v>
       </c>
       <c r="B164" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>135892055</v>
       </c>
       <c r="B165" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>135892058</v>
       </c>
       <c r="B166" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>135892059</v>
       </c>
       <c r="B167" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>135892062</v>
       </c>
       <c r="B168" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>135892065</v>
       </c>
       <c r="B169" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>135892074</v>
       </c>
       <c r="B170" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>135892075</v>
       </c>
       <c r="B171" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135892078</v>
       </c>
       <c r="B172" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>135905048</v>
       </c>
       <c r="B173" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>135905512</v>
       </c>
       <c r="B174" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>135905520</v>
       </c>
       <c r="B175" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>135905528</v>
       </c>
       <c r="B176" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>135905535</v>
       </c>
       <c r="B177" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>135905540</v>
       </c>
       <c r="B178" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>135905548</v>
       </c>
       <c r="B179" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>135905550</v>
       </c>
       <c r="B180" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>135905557</v>
       </c>
       <c r="B181" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>135905569</v>
       </c>
       <c r="B182" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>135905571</v>
       </c>
       <c r="B183" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>135905581</v>
       </c>
       <c r="B184" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>135905583</v>
       </c>
       <c r="B185" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>135905586</v>
       </c>
       <c r="B186" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>135892093</v>
       </c>
       <c r="B199" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>135892096</v>
       </c>
       <c r="B200" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>135892103</v>
       </c>
       <c r="B201" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>135892105</v>
       </c>
       <c r="B202" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>135905069</v>
       </c>
       <c r="B203" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -23090,7 +23090,7 @@
         <v>135905587</v>
       </c>
       <c r="B204" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>135905595</v>
       </c>
       <c r="B205" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>135905596</v>
       </c>
       <c r="B206" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>135905604</v>
       </c>
       <c r="B207" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>135905609</v>
       </c>
       <c r="B208" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>135892106</v>
       </c>
       <c r="B211" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>135905057</v>
       </c>
       <c r="B212" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>135905611</v>
       </c>
       <c r="B213" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>135892050</v>
       </c>
       <c r="B262" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>135892090</v>
       </c>
       <c r="B263" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>135892104</v>
       </c>
       <c r="B264" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>135892110</v>
       </c>
       <c r="B265" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>135892112</v>
       </c>
       <c r="B266" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>135894352</v>
       </c>
       <c r="B267" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>135905061</v>
       </c>
       <c r="B268" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>135905064</v>
       </c>
       <c r="B269" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>135905071</v>
       </c>
       <c r="B270" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>135905072</v>
       </c>
       <c r="B271" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>135905073</v>
       </c>
       <c r="B272" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>135905524</v>
       </c>
       <c r="B273" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>135905532</v>
       </c>
       <c r="B274" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>135905542</v>
       </c>
       <c r="B275" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>135905549</v>
       </c>
       <c r="B276" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>135905558</v>
       </c>
       <c r="B277" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>135905577</v>
       </c>
       <c r="B278" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>135905580</v>
       </c>
       <c r="B279" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>135905582</v>
       </c>
       <c r="B280" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>135905589</v>
       </c>
       <c r="B281" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>135905591</v>
       </c>
       <c r="B282" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>135905592</v>
       </c>
       <c r="B283" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>135905598</v>
       </c>
       <c r="B284" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>135905599</v>
       </c>
       <c r="B285" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>135905601</v>
       </c>
       <c r="B286" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>135905602</v>
       </c>
       <c r="B287" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135905605</v>
       </c>
       <c r="B288" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135905606</v>
       </c>
       <c r="B289" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>135905608</v>
       </c>
       <c r="B290" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>135905614</v>
       </c>
       <c r="B291" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>135905517</v>
       </c>
       <c r="B292" t="n">
-        <v>104061</v>
+        <v>104062</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>135892006</v>
       </c>
       <c r="B294" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135892015</v>
       </c>
       <c r="B295" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>135892044</v>
       </c>
       <c r="B296" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>135892072</v>
       </c>
       <c r="B297" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>135905040</v>
       </c>
       <c r="B298" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>135905047</v>
       </c>
       <c r="B299" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>135905053</v>
       </c>
       <c r="B300" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>135905054</v>
       </c>
       <c r="B301" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>135905056</v>
       </c>
       <c r="B302" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>135905058</v>
       </c>
       <c r="B303" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>135905066</v>
       </c>
       <c r="B304" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
@@ -34200,7 +34200,7 @@
         <v>135905067</v>
       </c>
       <c r="B305" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Nora Toftgård Shahnavaz, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe, Tilde Carlinger, Nora Toftgård Shahnavaz, Malte Lindberg, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
@@ -34316,7 +34316,7 @@
         <v>135905509</v>
       </c>
       <c r="B306" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>135905514</v>
       </c>
       <c r="B307" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>135905521</v>
       </c>
       <c r="B308" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>135905527</v>
       </c>
       <c r="B309" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>135905534</v>
       </c>
       <c r="B310" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>135905539</v>
       </c>
       <c r="B311" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>135905544</v>
       </c>
       <c r="B312" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>135905545</v>
       </c>
       <c r="B313" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>135905552</v>
       </c>
       <c r="B314" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>135905556</v>
       </c>
       <c r="B315" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>135905561</v>
       </c>
       <c r="B316" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>135905566</v>
       </c>
       <c r="B317" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>135905570</v>
       </c>
       <c r="B318" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>135905575</v>
       </c>
       <c r="B319" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>135905578</v>
       </c>
       <c r="B320" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>135905615</v>
       </c>
       <c r="B321" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>135892019</v>
       </c>
       <c r="B326" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>135892053</v>
       </c>
       <c r="B327" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>135892084</v>
       </c>
       <c r="B328" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>135905049</v>
       </c>
       <c r="B329" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>135905568</v>
       </c>
       <c r="B330" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
